--- a/Personel_Devam_Cizelgesi_Eylul_2026_FURKAN_BAYKUSAK.xlsx
+++ b/Personel_Devam_Cizelgesi_Eylul_2026_FURKAN_BAYKUSAK.xlsx
@@ -1814,7 +1814,7 @@
       </c>
       <c r="C43" s="28" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D43" s="6" t="n"/>
@@ -1824,7 +1824,7 @@
       <c r="H43" s="6" t="n"/>
       <c r="I43" s="28" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J43" s="9" t="n"/>
